--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/101.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/101.xlsx
@@ -426,13 +426,13 @@
         <v>4.455445430638882</v>
       </c>
       <c r="E2">
-        <v>-9.655863421932761</v>
+        <v>-8.55243733132777</v>
       </c>
       <c r="F2">
-        <v>-4.863845502994696</v>
+        <v>-5.286045315751339</v>
       </c>
       <c r="G2">
-        <v>-5.728250492805598</v>
+        <v>-6.832365141450948</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.236842087863304</v>
       </c>
       <c r="E3">
-        <v>-9.870331950936029</v>
+        <v>-10.04759906596628</v>
       </c>
       <c r="F3">
-        <v>-4.974552664541836</v>
+        <v>-5.408621325445791</v>
       </c>
       <c r="G3">
-        <v>-5.965318750475479</v>
+        <v>-8.090346112683338</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.042361841554673</v>
       </c>
       <c r="E4">
-        <v>-10.73292473686509</v>
+        <v>-11.74926827230258</v>
       </c>
       <c r="F4">
-        <v>-4.754549879501926</v>
+        <v>-5.097768173871248</v>
       </c>
       <c r="G4">
-        <v>-6.296889470278927</v>
+        <v>-7.777616167074222</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.913515426336503</v>
       </c>
       <c r="E5">
-        <v>-10.89165680778195</v>
+        <v>-11.65219590347416</v>
       </c>
       <c r="F5">
-        <v>-4.663246395997962</v>
+        <v>-5.731582723347054</v>
       </c>
       <c r="G5">
-        <v>-6.543240303740477</v>
+        <v>-8.121064908922861</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.85774672031991</v>
       </c>
       <c r="E6">
-        <v>-11.98404247875624</v>
+        <v>-11.51083958732473</v>
       </c>
       <c r="F6">
-        <v>-4.571778895748244</v>
+        <v>-4.60319638623422</v>
       </c>
       <c r="G6">
-        <v>-5.800187994274864</v>
+        <v>-7.441560017399014</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.895448564323851</v>
       </c>
       <c r="E7">
-        <v>-12.33230930079014</v>
+        <v>-11.42853457223532</v>
       </c>
       <c r="F7">
-        <v>-4.116540477498345</v>
+        <v>-5.339195025049762</v>
       </c>
       <c r="G7">
-        <v>-5.685807891934181</v>
+        <v>-8.132385123302944</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>4.035424272937457</v>
       </c>
       <c r="E8">
-        <v>-12.69057046495896</v>
+        <v>-13.168804491013</v>
       </c>
       <c r="F8">
-        <v>-4.200474804587005</v>
+        <v>-5.428662018021719</v>
       </c>
       <c r="G8">
-        <v>-6.060917140609901</v>
+        <v>-6.441653684260069</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>4.273865532994332</v>
       </c>
       <c r="E9">
-        <v>-13.07933543004346</v>
+        <v>-13.28129178536353</v>
       </c>
       <c r="F9">
-        <v>-4.318262022325872</v>
+        <v>-5.363643460575986</v>
       </c>
       <c r="G9">
-        <v>-5.605975771392891</v>
+        <v>-7.095811139237205</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.606644147735116</v>
       </c>
       <c r="E10">
-        <v>-15.039145768713</v>
+        <v>-13.44139145543071</v>
       </c>
       <c r="F10">
-        <v>-3.982380578043145</v>
+        <v>-5.041896449287227</v>
       </c>
       <c r="G10">
-        <v>-5.536755121374846</v>
+        <v>-6.590027241956599</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>5.02411411828882</v>
       </c>
       <c r="E11">
-        <v>-15.40197616315556</v>
+        <v>-14.41232798199329</v>
       </c>
       <c r="F11">
-        <v>-4.003533768041033</v>
+        <v>-4.568543292672909</v>
       </c>
       <c r="G11">
-        <v>-5.69190112037007</v>
+        <v>-6.762419341468265</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>5.497914089376189</v>
       </c>
       <c r="E12">
-        <v>-15.6393361282676</v>
+        <v>-15.21871787701316</v>
       </c>
       <c r="F12">
-        <v>-4.09012135592086</v>
+        <v>-4.376373652367063</v>
       </c>
       <c r="G12">
-        <v>-4.793912810089037</v>
+        <v>-6.929197270891721</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>6.004752138859392</v>
       </c>
       <c r="E13">
-        <v>-15.98557419394606</v>
+        <v>-15.34615819253702</v>
       </c>
       <c r="F13">
-        <v>-3.891561689469818</v>
+        <v>-4.347654154512004</v>
       </c>
       <c r="G13">
-        <v>-5.004960980792521</v>
+        <v>-5.642131551756412</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.520625972087847</v>
       </c>
       <c r="E14">
-        <v>-17.62195639051378</v>
+        <v>-15.56960215702349</v>
       </c>
       <c r="F14">
-        <v>-3.595658912781001</v>
+        <v>-4.031406674410431</v>
       </c>
       <c r="G14">
-        <v>-4.935107055013503</v>
+        <v>-5.403107686037103</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>7.010684197479694</v>
       </c>
       <c r="E15">
-        <v>-18.35300606346803</v>
+        <v>-17.4595517271767</v>
       </c>
       <c r="F15">
-        <v>-3.356840590553904</v>
+        <v>-4.60095648077705</v>
       </c>
       <c r="G15">
-        <v>-4.016624234872179</v>
+        <v>-5.258628938331633</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.450812678886649</v>
       </c>
       <c r="E16">
-        <v>-18.68311370473117</v>
+        <v>-19.31352709981297</v>
       </c>
       <c r="F16">
-        <v>-2.978284971148558</v>
+        <v>-2.885489597952152</v>
       </c>
       <c r="G16">
-        <v>-3.699566358026155</v>
+        <v>-5.09951594247104</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.823980793005973</v>
       </c>
       <c r="E17">
-        <v>-20.06291256402428</v>
+        <v>-18.49326648890761</v>
       </c>
       <c r="F17">
-        <v>-2.73946664892146</v>
+        <v>-3.810056135606167</v>
       </c>
       <c r="G17">
-        <v>-3.811797260245402</v>
+        <v>-5.505281644176652</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.109309901066759</v>
       </c>
       <c r="E18">
-        <v>-20.5323975782955</v>
+        <v>-19.54194332875986</v>
       </c>
       <c r="F18">
-        <v>-2.729700197242454</v>
+        <v>-3.043091466539174</v>
       </c>
       <c r="G18">
-        <v>-3.301741212494399</v>
+        <v>-5.170209860969276</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.295000584659652</v>
       </c>
       <c r="E19">
-        <v>-21.30801649243325</v>
+        <v>-22.55813797004271</v>
       </c>
       <c r="F19">
-        <v>-2.278735326423598</v>
+        <v>-2.900837589191221</v>
       </c>
       <c r="G19">
-        <v>-3.093173645289855</v>
+        <v>-5.101238583789748</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.38148454166214</v>
       </c>
       <c r="E20">
-        <v>-22.51205621854066</v>
+        <v>-22.32964022856368</v>
       </c>
       <c r="F20">
-        <v>-1.808873738412079</v>
+        <v>-2.619292076327725</v>
       </c>
       <c r="G20">
-        <v>-3.403826577651843</v>
+        <v>-5.02547517798217</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.369423178991909</v>
       </c>
       <c r="E21">
-        <v>-22.92653838751471</v>
+        <v>-23.40708646378667</v>
       </c>
       <c r="F21">
-        <v>-1.566857918010175</v>
+        <v>-2.778300512764701</v>
       </c>
       <c r="G21">
-        <v>-3.162085860481313</v>
+        <v>-4.220945901378801</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.263972365110693</v>
       </c>
       <c r="E22">
-        <v>-22.94638668909033</v>
+        <v>-22.78558963402597</v>
       </c>
       <c r="F22">
-        <v>-1.401187750919886</v>
+        <v>-2.254682850515911</v>
       </c>
       <c r="G22">
-        <v>-2.90665588696478</v>
+        <v>-5.187610178899011</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.082707684745564</v>
       </c>
       <c r="E23">
-        <v>-23.62041834581401</v>
+        <v>-24.18645042592876</v>
       </c>
       <c r="F23">
-        <v>-1.231686384591648</v>
+        <v>-1.865161303432305</v>
       </c>
       <c r="G23">
-        <v>-3.662737927242947</v>
+        <v>-3.992041322948819</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.84331585919309</v>
       </c>
       <c r="E24">
-        <v>-24.2782788218563</v>
+        <v>-24.11629983507594</v>
       </c>
       <c r="F24">
-        <v>-0.9537616656457886</v>
+        <v>-1.989292158741811</v>
       </c>
       <c r="G24">
-        <v>-3.45371427024164</v>
+        <v>-4.303695027886437</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.560868100181687</v>
       </c>
       <c r="E25">
-        <v>-24.02853348033328</v>
+        <v>-21.06604201230739</v>
       </c>
       <c r="F25">
-        <v>-0.894024778760305</v>
+        <v>-1.834690636887728</v>
       </c>
       <c r="G25">
-        <v>-3.084022318360564</v>
+        <v>-5.558250403810768</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.259355495167959</v>
       </c>
       <c r="E26">
-        <v>-24.63141828192245</v>
+        <v>-24.88083757331692</v>
       </c>
       <c r="F26">
-        <v>-0.6085420356313029</v>
+        <v>-1.213536026428908</v>
       </c>
       <c r="G26">
-        <v>-3.890415328809697</v>
+        <v>-4.298766633104152</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.962100316158707</v>
       </c>
       <c r="E27">
-        <v>-24.59509992038093</v>
+        <v>-23.37633812527459</v>
       </c>
       <c r="F27">
-        <v>-0.8651255251788387</v>
+        <v>-0.672796838331655</v>
       </c>
       <c r="G27">
-        <v>-3.54010883390182</v>
+        <v>-4.453952006758089</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.682977182634403</v>
       </c>
       <c r="E28">
-        <v>-24.09171022121429</v>
+        <v>-24.8800043340995</v>
       </c>
       <c r="F28">
-        <v>-1.013695703973138</v>
+        <v>-1.26094846309554</v>
       </c>
       <c r="G28">
-        <v>-3.995273326184872</v>
+        <v>-5.08816619709692</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.441548488599042</v>
       </c>
       <c r="E29">
-        <v>-23.58967453577593</v>
+        <v>-24.91372335156062</v>
       </c>
       <c r="F29">
-        <v>-0.7798823775937554</v>
+        <v>-1.23514896033535</v>
       </c>
       <c r="G29">
-        <v>-4.748592577909987</v>
+        <v>-3.991060237702545</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.256958962909403</v>
       </c>
       <c r="E30">
-        <v>-22.74930750027652</v>
+        <v>-21.88215906949574</v>
       </c>
       <c r="F30">
-        <v>-1.014275561155098</v>
+        <v>-1.049205329428945</v>
       </c>
       <c r="G30">
-        <v>-4.966573969768578</v>
+        <v>-5.904133812056513</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.130856330311754</v>
       </c>
       <c r="E31">
-        <v>-23.15428893078248</v>
+        <v>-23.47232818881517</v>
       </c>
       <c r="F31">
-        <v>-0.7447372337951809</v>
+        <v>-1.695979686921548</v>
       </c>
       <c r="G31">
-        <v>-3.913534815917544</v>
+        <v>-5.573685270026396</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.066156358999232</v>
       </c>
       <c r="E32">
-        <v>-22.45962101800584</v>
+        <v>-22.65559978763579</v>
       </c>
       <c r="F32">
-        <v>-1.232572737712643</v>
+        <v>-1.528811003199594</v>
       </c>
       <c r="G32">
-        <v>-4.437293244900788</v>
+        <v>-6.411715818751695</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.067904355506674</v>
       </c>
       <c r="E33">
-        <v>-21.02038593736206</v>
+        <v>-22.38251016260323</v>
       </c>
       <c r="F33">
-        <v>-0.9480749234255699</v>
+        <v>-1.161356335359164</v>
       </c>
       <c r="G33">
-        <v>-4.411141909072014</v>
+        <v>-6.674928849807231</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.121734979456446</v>
       </c>
       <c r="E34">
-        <v>-20.80738916241128</v>
+        <v>-20.8699772016713</v>
       </c>
       <c r="F34">
-        <v>-0.9928258156270077</v>
+        <v>-1.337115189048149</v>
       </c>
       <c r="G34">
-        <v>-4.081510391210198</v>
+        <v>-4.793099067142295</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.216969788357749</v>
       </c>
       <c r="E35">
-        <v>-20.62047639774469</v>
+        <v>-19.13923519220575</v>
       </c>
       <c r="F35">
-        <v>-1.338953336314961</v>
+        <v>-1.387057459762931</v>
       </c>
       <c r="G35">
-        <v>-5.5184655924025</v>
+        <v>-5.475363465997635</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.349112043654202</v>
       </c>
       <c r="E36">
-        <v>-19.56243014517056</v>
+        <v>-19.23793328320293</v>
       </c>
       <c r="F36">
-        <v>-1.32008064177698</v>
+        <v>-1.533051415934525</v>
       </c>
       <c r="G36">
-        <v>-4.792177043884091</v>
+        <v>-5.800827832478956</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.500035588769022</v>
       </c>
       <c r="E37">
-        <v>-19.02416213919684</v>
+        <v>-19.3492612882075</v>
       </c>
       <c r="F37">
-        <v>-1.275457318155574</v>
+        <v>-1.292660024009511</v>
       </c>
       <c r="G37">
-        <v>-5.222033474279146</v>
+        <v>-6.958567485070311</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.655185094205722</v>
       </c>
       <c r="E38">
-        <v>-18.38960519039803</v>
+        <v>-17.35915545842665</v>
       </c>
       <c r="F38">
-        <v>-1.589550214642465</v>
+        <v>-2.458901094695476</v>
       </c>
       <c r="G38">
-        <v>-5.350969075457527</v>
+        <v>-7.174150303968948</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>6.80966193710779</v>
       </c>
       <c r="E39">
-        <v>-19.15298816776705</v>
+        <v>-17.45490551284482</v>
       </c>
       <c r="F39">
-        <v>-1.236636708190778</v>
+        <v>-2.397620959338577</v>
       </c>
       <c r="G39">
-        <v>-5.471701622737294</v>
+        <v>-6.974189380914827</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.951424915052069</v>
       </c>
       <c r="E40">
-        <v>-17.92345313299645</v>
+        <v>-16.55243951327822</v>
       </c>
       <c r="F40">
-        <v>-1.719239415224756</v>
+        <v>-2.433384893587043</v>
       </c>
       <c r="G40">
-        <v>-4.994254354844053</v>
+        <v>-6.281310230314683</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>7.070951252469171</v>
       </c>
       <c r="E41">
-        <v>-17.79374405199475</v>
+        <v>-16.18196505471071</v>
       </c>
       <c r="F41">
-        <v>-1.842304161686859</v>
+        <v>-1.927923388072813</v>
       </c>
       <c r="G41">
-        <v>-4.640039925058877</v>
+        <v>-6.089030646931223</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>7.170052545524902</v>
       </c>
       <c r="E42">
-        <v>-15.74001769088014</v>
+        <v>-15.27406941480891</v>
       </c>
       <c r="F42">
-        <v>-1.653120785868105</v>
+        <v>-2.446449075896594</v>
       </c>
       <c r="G42">
-        <v>-4.675227745062362</v>
+        <v>-6.965996170680894</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>7.24632770938553</v>
       </c>
       <c r="E43">
-        <v>-15.32962473393501</v>
+        <v>-13.35977929686448</v>
       </c>
       <c r="F43">
-        <v>-1.75270960013487</v>
+        <v>-2.12477744604149</v>
       </c>
       <c r="G43">
-        <v>-4.54229233480302</v>
+        <v>-6.268159094304429</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>7.294998864052732</v>
       </c>
       <c r="E44">
-        <v>-14.64058571434991</v>
+        <v>-15.69010032189359</v>
       </c>
       <c r="F44">
-        <v>-1.669333592675697</v>
+        <v>-1.848999855403687</v>
       </c>
       <c r="G44">
-        <v>-5.131448790687556</v>
+        <v>-6.391057247813431</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>7.321218819870144</v>
       </c>
       <c r="E45">
-        <v>-13.35261072251033</v>
+        <v>-14.2026868062822</v>
       </c>
       <c r="F45">
-        <v>-1.997575832769806</v>
+        <v>-2.016777389166699</v>
       </c>
       <c r="G45">
-        <v>-4.963184467897672</v>
+        <v>-6.585075878623397</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>7.328013630272947</v>
       </c>
       <c r="E46">
-        <v>-13.83438601523837</v>
+        <v>-12.3763305966187</v>
       </c>
       <c r="F46">
-        <v>-1.683184724017907</v>
+        <v>-2.225386808948504</v>
       </c>
       <c r="G46">
-        <v>-4.973228287091132</v>
+        <v>-7.144652122149539</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>7.3124937103744</v>
       </c>
       <c r="E47">
-        <v>-12.31631020212104</v>
+        <v>-12.0644862910285</v>
       </c>
       <c r="F47">
-        <v>-1.864590558291777</v>
+        <v>-2.145343323550793</v>
       </c>
       <c r="G47">
-        <v>-4.75401315592619</v>
+        <v>-5.127084766013494</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>7.281087455662344</v>
       </c>
       <c r="E48">
-        <v>-12.0000144065813</v>
+        <v>-11.13490831757798</v>
       </c>
       <c r="F48">
-        <v>-1.850948175535071</v>
+        <v>-2.074116980788481</v>
       </c>
       <c r="G48">
-        <v>-4.113154491929483</v>
+        <v>-5.165530839025508</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>7.241502487838878</v>
       </c>
       <c r="E49">
-        <v>-10.63094350221236</v>
+        <v>-9.305708226237664</v>
       </c>
       <c r="F49">
-        <v>-2.12995557067639</v>
+        <v>-2.654056999488414</v>
       </c>
       <c r="G49">
-        <v>-4.651511075630697</v>
+        <v>-5.567067046140996</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>7.192139711853644</v>
       </c>
       <c r="E50">
-        <v>-10.34581719326741</v>
+        <v>-9.047911257929007</v>
       </c>
       <c r="F50">
-        <v>-2.346053431779502</v>
+        <v>-2.400765441999604</v>
       </c>
       <c r="G50">
-        <v>-4.903407173527707</v>
+        <v>-7.379013372032878</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>7.138343508026827</v>
       </c>
       <c r="E51">
-        <v>-9.473972734940672</v>
+        <v>-8.168581232067591</v>
       </c>
       <c r="F51">
-        <v>-2.117950870275019</v>
+        <v>-2.459423794526643</v>
       </c>
       <c r="G51">
-        <v>-4.176948001488207</v>
+        <v>-5.223884083238673</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>7.08879219383272</v>
       </c>
       <c r="E52">
-        <v>-8.166846826522654</v>
+        <v>-8.243667859588774</v>
       </c>
       <c r="F52">
-        <v>-2.32734309725247</v>
+        <v>-2.818873948153821</v>
       </c>
       <c r="G52">
-        <v>-4.857099293659264</v>
+        <v>-6.952812222455044</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>7.038742469700063</v>
       </c>
       <c r="E53">
-        <v>-7.979816321531861</v>
+        <v>-7.126325768358213</v>
       </c>
       <c r="F53">
-        <v>-2.309341845222234</v>
+        <v>-2.813973326598859</v>
       </c>
       <c r="G53">
-        <v>-4.191017879535106</v>
+        <v>-7.001810704002232</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.988457439145303</v>
       </c>
       <c r="E54">
-        <v>-7.683762804806404</v>
+        <v>-7.033578092207117</v>
       </c>
       <c r="F54">
-        <v>-2.160119741281931</v>
+        <v>-2.240380258939175</v>
       </c>
       <c r="G54">
-        <v>-5.174242482265834</v>
+        <v>-5.716139504029688</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.944422448560514</v>
       </c>
       <c r="E55">
-        <v>-6.521638634113991</v>
+        <v>-9.568744638973198</v>
       </c>
       <c r="F55">
-        <v>-1.822821788740417</v>
+        <v>-2.718924794066838</v>
       </c>
       <c r="G55">
-        <v>-3.993731152051933</v>
+        <v>-6.352000867591361</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>6.899479250156459</v>
       </c>
       <c r="E56">
-        <v>-7.869733646879403</v>
+        <v>-4.722593651190757</v>
       </c>
       <c r="F56">
-        <v>-2.46804544245498</v>
+        <v>-3.351770153681368</v>
       </c>
       <c r="G56">
-        <v>-4.811992340881578</v>
+        <v>-6.264142879115669</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>6.849606738740744</v>
       </c>
       <c r="E57">
-        <v>-5.695296282616327</v>
+        <v>-5.693892455673949</v>
       </c>
       <c r="F57">
-        <v>-1.816008466852391</v>
+        <v>-2.495954796990101</v>
       </c>
       <c r="G57">
-        <v>-4.084365053966915</v>
+        <v>-4.698258639188105</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>6.799218247821862</v>
       </c>
       <c r="E58">
-        <v>-5.442426294028014</v>
+        <v>-3.942459848467362</v>
       </c>
       <c r="F58">
-        <v>-2.385546676075371</v>
+        <v>-2.954036172166408</v>
       </c>
       <c r="G58">
-        <v>-4.933715817072298</v>
+        <v>-6.392966918761028</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>6.743388904794582</v>
       </c>
       <c r="E59">
-        <v>-4.429556098154408</v>
+        <v>-6.01071808267259</v>
       </c>
       <c r="F59">
-        <v>-2.403853595677241</v>
+        <v>-2.867059251607265</v>
       </c>
       <c r="G59">
-        <v>-4.865883123773898</v>
+        <v>-6.036764068710829</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>6.679175212540817</v>
       </c>
       <c r="E60">
-        <v>-3.860526168246582</v>
+        <v>-2.932456176640611</v>
       </c>
       <c r="F60">
-        <v>-2.308732166813773</v>
+        <v>-3.051202840147387</v>
       </c>
       <c r="G60">
-        <v>-4.930480532614686</v>
+        <v>-7.000508059043133</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>6.614860884769646</v>
       </c>
       <c r="E61">
-        <v>-4.350878390745144</v>
+        <v>-4.136591000702182</v>
       </c>
       <c r="F61">
-        <v>-2.095370403242108</v>
+        <v>-2.761840852471075</v>
       </c>
       <c r="G61">
-        <v>-5.154988274155012</v>
+        <v>-6.135246652596003</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>6.553050691293122</v>
       </c>
       <c r="E62">
-        <v>-3.707948293506144</v>
+        <v>-3.064574405814394</v>
       </c>
       <c r="F62">
-        <v>-2.672344038272616</v>
+        <v>-3.216322971282218</v>
       </c>
       <c r="G62">
-        <v>-5.170725012754109</v>
+        <v>-6.301611148102968</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>6.494993482439803</v>
       </c>
       <c r="E63">
-        <v>-2.804282248327509</v>
+        <v>-3.852682851265297</v>
       </c>
       <c r="F63">
-        <v>-2.481862610733676</v>
+        <v>-3.584386489163706</v>
       </c>
       <c r="G63">
-        <v>-4.871562918293296</v>
+        <v>-6.296548223236745</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>6.453436020955493</v>
       </c>
       <c r="E64">
-        <v>-2.918644330917216</v>
+        <v>-3.433604281173459</v>
       </c>
       <c r="F64">
-        <v>-2.519931891464132</v>
+        <v>-3.185182155508776</v>
       </c>
       <c r="G64">
-        <v>-5.072127586114354</v>
+        <v>-6.263053513557933</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>6.437092817005141</v>
       </c>
       <c r="E65">
-        <v>-2.138284104493438</v>
+        <v>-2.376332397654645</v>
       </c>
       <c r="F65">
-        <v>-2.883764937019523</v>
+        <v>-3.50974147413004</v>
       </c>
       <c r="G65">
-        <v>-5.11747734928744</v>
+        <v>-5.361275392375742</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>6.447647187767521</v>
       </c>
       <c r="E66">
-        <v>-2.441904701285712</v>
+        <v>-2.890803272718059</v>
       </c>
       <c r="F66">
-        <v>-2.53922953847975</v>
+        <v>-3.377156301107562</v>
       </c>
       <c r="G66">
-        <v>-4.230727222847506</v>
+        <v>-5.421997678554826</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>6.496406961248904</v>
       </c>
       <c r="E67">
-        <v>-3.008629637923634</v>
+        <v>-1.764413290420173</v>
       </c>
       <c r="F67">
-        <v>-2.828912104340946</v>
+        <v>-3.283057905986552</v>
       </c>
       <c r="G67">
-        <v>-5.045831876536965</v>
+        <v>-5.475940960992097</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>6.59113239740526</v>
       </c>
       <c r="E68">
-        <v>-2.959726647114802</v>
+        <v>-1.716796386229519</v>
       </c>
       <c r="F68">
-        <v>-3.105702788312372</v>
+        <v>-3.614456225885328</v>
       </c>
       <c r="G68">
-        <v>-5.11895389898919</v>
+        <v>-5.637577216231903</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>6.72629455951383</v>
       </c>
       <c r="E69">
-        <v>-2.51196472265838</v>
+        <v>-3.337863283703292</v>
       </c>
       <c r="F69">
-        <v>-2.868169263927017</v>
+        <v>-3.551773664515489</v>
       </c>
       <c r="G69">
-        <v>-4.759249985535063</v>
+        <v>-5.924782539330099</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>6.904954732689206</v>
       </c>
       <c r="E70">
-        <v>-2.300752166466627</v>
+        <v>-2.218669046603594</v>
       </c>
       <c r="F70">
-        <v>-3.485857156805122</v>
+        <v>-3.436818634926794</v>
       </c>
       <c r="G70">
-        <v>-4.548815403263196</v>
+        <v>-5.671311455084554</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>7.130003321528496</v>
       </c>
       <c r="E71">
-        <v>-2.275089304265159</v>
+        <v>-3.276357549731113</v>
       </c>
       <c r="F71">
-        <v>-3.085585057567983</v>
+        <v>-3.987356581031761</v>
       </c>
       <c r="G71">
-        <v>-4.83413730518627</v>
+        <v>-5.672650193480807</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>7.388074812790633</v>
       </c>
       <c r="E72">
-        <v>-2.560749973143013</v>
+        <v>-3.711317478167851</v>
       </c>
       <c r="F72">
-        <v>-3.639831604535285</v>
+        <v>-3.499700004473304</v>
       </c>
       <c r="G72">
-        <v>-4.331467287165577</v>
+        <v>-5.051367297307748</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>7.675635808546412</v>
       </c>
       <c r="E73">
-        <v>-2.523815739136453</v>
+        <v>-3.822704353334519</v>
       </c>
       <c r="F73">
-        <v>-3.427845759219669</v>
+        <v>-4.138533632042671</v>
       </c>
       <c r="G73">
-        <v>-3.805254504455869</v>
+        <v>-5.595305238881577</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>7.992507999841041</v>
       </c>
       <c r="E74">
-        <v>-2.398703059252536</v>
+        <v>-3.317521378460837</v>
       </c>
       <c r="F74">
-        <v>-3.562152279705164</v>
+        <v>-3.804379333794782</v>
       </c>
       <c r="G74">
-        <v>-3.659459986905062</v>
+        <v>-5.66105435648973</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>8.321145585812957</v>
       </c>
       <c r="E75">
-        <v>-3.511059300600653</v>
+        <v>-1.939008605785903</v>
       </c>
       <c r="F75">
-        <v>-3.677917452613798</v>
+        <v>-4.120736158393524</v>
       </c>
       <c r="G75">
-        <v>-4.068388786193979</v>
+        <v>-5.026157672066534</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>8.654034666101168</v>
       </c>
       <c r="E76">
-        <v>-4.213978093019261</v>
+        <v>-3.881103554137436</v>
       </c>
       <c r="F76">
-        <v>-3.696895349811935</v>
+        <v>-4.538447048194397</v>
       </c>
       <c r="G76">
-        <v>-3.362132095295979</v>
+        <v>-3.802609839878957</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>8.989366887697793</v>
       </c>
       <c r="E77">
-        <v>-4.293063363089216</v>
+        <v>-5.634981537308165</v>
       </c>
       <c r="F77">
-        <v>-3.847089128715721</v>
+        <v>-4.530607379094302</v>
       </c>
       <c r="G77">
-        <v>-3.190947485318189</v>
+        <v>-3.982141877503974</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>9.311638201242857</v>
       </c>
       <c r="E78">
-        <v>-4.408679832979048</v>
+        <v>-5.457854804972147</v>
       </c>
       <c r="F78">
-        <v>-3.475353458137624</v>
+        <v>-4.363563778850171</v>
       </c>
       <c r="G78">
-        <v>-2.335887396699371</v>
+        <v>-4.32093456595976</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>9.610736792334855</v>
       </c>
       <c r="E79">
-        <v>-5.380485826551099</v>
+        <v>-5.925360876102012</v>
       </c>
       <c r="F79">
-        <v>-4.037946635055533</v>
+        <v>-4.38563148646075</v>
       </c>
       <c r="G79">
-        <v>-2.318086769739384</v>
+        <v>-2.82977686582699</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>9.885242319332589</v>
       </c>
       <c r="E80">
-        <v>-6.748986143195073</v>
+        <v>-5.679283598525204</v>
       </c>
       <c r="F80">
-        <v>-4.430796562363588</v>
+        <v>-3.817882550827816</v>
       </c>
       <c r="G80">
-        <v>-2.107150160568921</v>
+        <v>-2.810309378314805</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>10.12344384352063</v>
       </c>
       <c r="E81">
-        <v>-7.10761411375852</v>
+        <v>-6.916951772613574</v>
       </c>
       <c r="F81">
-        <v>-4.134901240981396</v>
+        <v>-5.248774581197182</v>
       </c>
       <c r="G81">
-        <v>-1.589603083997706</v>
+        <v>-2.095012922020535</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>10.31387058407744</v>
       </c>
       <c r="E82">
-        <v>-7.140019873757408</v>
+        <v>-10.47526362277667</v>
       </c>
       <c r="F82">
-        <v>-4.095923241210068</v>
+        <v>-4.619001636279635</v>
       </c>
       <c r="G82">
-        <v>-1.82074217430967</v>
+        <v>-1.353000759789266</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>10.45648943901498</v>
       </c>
       <c r="E83">
-        <v>-9.496569820238948</v>
+        <v>-9.173965860406518</v>
       </c>
       <c r="F83">
-        <v>-4.501457130189788</v>
+        <v>-5.073726466739799</v>
       </c>
       <c r="G83">
-        <v>-0.7614194811723001</v>
+        <v>-1.706040512256161</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>10.54567095236481</v>
       </c>
       <c r="E84">
-        <v>-9.878161682495291</v>
+        <v>-8.79366914171637</v>
       </c>
       <c r="F84">
-        <v>-4.528787455910352</v>
+        <v>-4.880130377766331</v>
       </c>
       <c r="G84">
-        <v>-0.7589191903440032</v>
+        <v>-2.022031992095366</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>10.57185147495181</v>
       </c>
       <c r="E85">
-        <v>-10.46989285260357</v>
+        <v>-12.90693642457145</v>
       </c>
       <c r="F85">
-        <v>-4.337473519131598</v>
+        <v>-5.105143128858373</v>
       </c>
       <c r="G85">
-        <v>-0.4536999608844557</v>
+        <v>-1.525839105433017</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>10.53779611884937</v>
       </c>
       <c r="E86">
-        <v>-11.39397325860878</v>
+        <v>-11.8500585182913</v>
       </c>
       <c r="F86">
-        <v>-4.762963607212161</v>
+        <v>-5.331832495573679</v>
       </c>
       <c r="G86">
-        <v>-0.2851862652560535</v>
+        <v>-0.7596148093146055</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>10.44584969300968</v>
       </c>
       <c r="E87">
-        <v>-12.64998628090222</v>
+        <v>-14.88418138817052</v>
       </c>
       <c r="F87">
-        <v>-4.966009711516765</v>
+        <v>-4.590929921733565</v>
       </c>
       <c r="G87">
-        <v>-0.15621128941896</v>
+        <v>-2.859898479742693</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>10.29124888212433</v>
       </c>
       <c r="E88">
-        <v>-15.13746346789353</v>
+        <v>-15.51410570805949</v>
       </c>
       <c r="F88">
-        <v>-4.830618858101005</v>
+        <v>-5.153471739872502</v>
       </c>
       <c r="G88">
-        <v>1.026235961515013</v>
+        <v>-0.2226330574467994</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>10.07911266370418</v>
       </c>
       <c r="E89">
-        <v>-16.60084437194621</v>
+        <v>-18.18510836115965</v>
       </c>
       <c r="F89">
-        <v>-5.215964605107099</v>
+        <v>-5.257889936097587</v>
       </c>
       <c r="G89">
-        <v>0.02312715613405035</v>
+        <v>-0.08059225735999712</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>9.818574275715529</v>
       </c>
       <c r="E90">
-        <v>-19.06790719811094</v>
+        <v>-17.08400084924659</v>
       </c>
       <c r="F90">
-        <v>-5.604562522536583</v>
+        <v>-5.090499249911683</v>
       </c>
       <c r="G90">
-        <v>-0.1257156162454808</v>
+        <v>0.04779209859639628</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>9.507391779179626</v>
       </c>
       <c r="E91">
-        <v>-19.41447131391795</v>
+        <v>-19.90193889847363</v>
       </c>
       <c r="F91">
-        <v>-5.928038336594985</v>
+        <v>-5.61166328791338</v>
       </c>
       <c r="G91">
-        <v>1.108765246178167</v>
+        <v>-1.16489160900786</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>9.147699766282333</v>
       </c>
       <c r="E92">
-        <v>-21.87047107808194</v>
+        <v>-22.24208218362537</v>
       </c>
       <c r="F92">
-        <v>-5.669464280178522</v>
+        <v>-6.079556674975848</v>
       </c>
       <c r="G92">
-        <v>-0.8473546738141572</v>
+        <v>-2.0257266475713</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>8.750582104028005</v>
       </c>
       <c r="E93">
-        <v>-23.51052133859586</v>
+        <v>-25.49061018387175</v>
       </c>
       <c r="F93">
-        <v>-5.842676732471301</v>
+        <v>-5.638800604029092</v>
       </c>
       <c r="G93">
-        <v>0.1150899527806074</v>
+        <v>-1.764600473427571</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>8.313167666239176</v>
       </c>
       <c r="E94">
-        <v>-24.93385241852471</v>
+        <v>-25.65652441456478</v>
       </c>
       <c r="F94">
-        <v>-6.141834164685718</v>
+        <v>-6.093298461820889</v>
       </c>
       <c r="G94">
-        <v>0.2114823985324148</v>
+        <v>-2.447245493983806</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.83572298628231</v>
       </c>
       <c r="E95">
-        <v>-26.78655076149083</v>
+        <v>-27.48705587726334</v>
       </c>
       <c r="F95">
-        <v>-6.129144404442232</v>
+        <v>-6.218856594165418</v>
       </c>
       <c r="G95">
-        <v>-1.33861916569422</v>
+        <v>-1.323407422544634</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.32725745911289</v>
       </c>
       <c r="E96">
-        <v>-29.89701917466536</v>
+        <v>-29.45878063104707</v>
       </c>
       <c r="F96">
-        <v>-6.442131430446386</v>
+        <v>-6.277943626823405</v>
       </c>
       <c r="G96">
-        <v>-0.5107341540307238</v>
+        <v>-3.140649640033461</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.794024191642777</v>
       </c>
       <c r="E97">
-        <v>-31.89241879056118</v>
+        <v>-31.16531568270461</v>
       </c>
       <c r="F97">
-        <v>-6.464965377904554</v>
+        <v>-6.553819793182142</v>
       </c>
       <c r="G97">
-        <v>-1.834001590631386</v>
+        <v>-1.503388987523296</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.22819861868722</v>
       </c>
       <c r="E98">
-        <v>-33.39601933651299</v>
+        <v>-34.42494297274378</v>
       </c>
       <c r="F98">
-        <v>-6.641710402986572</v>
+        <v>-6.802030973389583</v>
       </c>
       <c r="G98">
-        <v>-2.581559017298116</v>
+        <v>-3.934196668077368</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.661406410180744</v>
       </c>
       <c r="E99">
-        <v>-35.00982935438947</v>
+        <v>-35.62736829786746</v>
       </c>
       <c r="F99">
-        <v>-6.923321356874889</v>
+        <v>-6.434058575922403</v>
       </c>
       <c r="G99">
-        <v>-2.956727327961906</v>
+        <v>-3.291077242426204</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>5.079434990430713</v>
       </c>
       <c r="E100">
-        <v>-37.54413549109409</v>
+        <v>-36.92385908507846</v>
       </c>
       <c r="F100">
-        <v>-7.086166791121633</v>
+        <v>-6.718360895502416</v>
       </c>
       <c r="G100">
-        <v>-3.962956575045901</v>
+        <v>-5.449077600084923</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.529434809408677</v>
       </c>
       <c r="E101">
-        <v>-39.99308894970214</v>
+        <v>-41.48657514895782</v>
       </c>
       <c r="F101">
-        <v>-7.189671712285133</v>
+        <v>-6.430803506213103</v>
       </c>
       <c r="G101">
-        <v>-4.435111232563758</v>
+        <v>-5.471642560749224</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.969370684410203</v>
       </c>
       <c r="E102">
-        <v>-43.00197916241062</v>
+        <v>-43.57857164391125</v>
       </c>
       <c r="F102">
-        <v>-7.156765645576325</v>
+        <v>-6.899444494856596</v>
       </c>
       <c r="G102">
-        <v>-5.095893473869413</v>
+        <v>-6.576810481515156</v>
       </c>
     </row>
   </sheetData>
